--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>数据类型（市场数据，供应链数据，经营数据，财务数据）</t>
+  </si>
   <si>
     <t>指标分类</t>
   </si>
@@ -41,14 +44,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,48 +502,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -557,97 +556,94 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1003,10 +999,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1022,6 +1021,9 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="年" sheetId="1" r:id="rId1"/>
@@ -13,25 +13,51 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+例如：2021年</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>数据类型（市场数据，供应链数据，经营数据，财务数据）</t>
+    <t>*数据类型</t>
   </si>
   <si>
-    <t>指标分类</t>
+    <t>*指标分类</t>
   </si>
   <si>
-    <t>指标名称</t>
+    <t>*指标名称</t>
   </si>
   <si>
-    <t>目标值</t>
-  </si>
-  <si>
-    <t>2021年</t>
-  </si>
-  <si>
-    <t>2022年</t>
+    <t>*目标值</t>
   </si>
 </sst>
 </file>
@@ -44,7 +70,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +221,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -999,13 +1036,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1018,16 +1055,21 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
+      <formula1>"市场数据,供应链数据,经营数据,财务数据"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomYear.xlsx
@@ -19,7 +19,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -37,7 +37,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-例如：2021年</t>
+例如：2023年</t>
         </r>
       </text>
     </comment>
@@ -46,18 +46,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>*数据类型</t>
+    <t>*年份</t>
   </si>
   <si>
-    <t>*指标分类</t>
+    <t>指标分类</t>
   </si>
   <si>
     <t>*指标名称</t>
   </si>
   <si>
     <t>*目标值</t>
+  </si>
+  <si>
+    <t>实际值</t>
   </si>
 </sst>
 </file>
@@ -1038,9 +1041,6 @@
   <sheetPr/>
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1055,16 +1055,19 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1"/>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>"市场数据,供应链数据,经营数据,财务数据"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+25</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
